--- a/PawPewPewTranslate.xlsx
+++ b/PawPewPewTranslate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Project Website\PawPewPew\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E06E1D0C-6BCC-4690-BB0E-0E655F32B8E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99148D5B-CDD1-4991-9231-012F15E5B679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{15B7F092-291F-47B8-BF64-7EB67EA1D344}"/>
+    <workbookView xWindow="5115" yWindow="1935" windowWidth="15375" windowHeight="9585" xr2:uid="{15B7F092-291F-47B8-BF64-7EB67EA1D344}"/>
   </bookViews>
   <sheets>
     <sheet name="Menu" sheetId="1" r:id="rId1"/>

--- a/PawPewPewTranslate.xlsx
+++ b/PawPewPewTranslate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Project Website\PawPewPew\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99148D5B-CDD1-4991-9231-012F15E5B679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B87B04A0-34CD-47A0-B58C-078BF5148D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5115" yWindow="1935" windowWidth="15375" windowHeight="9585" xr2:uid="{15B7F092-291F-47B8-BF64-7EB67EA1D344}"/>
   </bookViews>
